--- a/output/manualisasi_tombert.xlsx
+++ b/output/manualisasi_tombert.xlsx
@@ -9,6 +9,7 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data_TomBERT" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ringkasan_Metrik" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Manual_Prediksi_TomBERT" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -39898,7 +39899,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J100"/>
+  <dimension ref="A1:H16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -39912,7 +39913,6 @@
         <v/>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
@@ -39935,7 +39935,6 @@
         <v/>
       </c>
     </row>
-    <row r="5"/>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
@@ -40127,7 +40126,6 @@
         <v/>
       </c>
     </row>
-    <row r="13"/>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
@@ -40161,90 +40159,449 @@
         <v/>
       </c>
     </row>
-    <row r="17"/>
-    <row r="18"/>
-    <row r="19"/>
-    <row r="20"/>
-    <row r="21"/>
-    <row r="22"/>
-    <row r="23"/>
-    <row r="24"/>
-    <row r="25"/>
-    <row r="26"/>
-    <row r="27"/>
-    <row r="28"/>
-    <row r="29"/>
-    <row r="30"/>
-    <row r="31"/>
-    <row r="32"/>
-    <row r="33"/>
-    <row r="34"/>
-    <row r="35"/>
-    <row r="36"/>
-    <row r="37"/>
-    <row r="38"/>
-    <row r="39"/>
-    <row r="40"/>
-    <row r="41"/>
-    <row r="42"/>
-    <row r="43"/>
-    <row r="44"/>
-    <row r="45"/>
-    <row r="46"/>
-    <row r="47"/>
-    <row r="48"/>
-    <row r="49"/>
-    <row r="50"/>
-    <row r="51"/>
-    <row r="52"/>
-    <row r="53"/>
-    <row r="54"/>
-    <row r="55"/>
-    <row r="56"/>
-    <row r="57"/>
-    <row r="58"/>
-    <row r="59"/>
-    <row r="60"/>
-    <row r="61"/>
-    <row r="62"/>
-    <row r="63"/>
-    <row r="64"/>
-    <row r="65"/>
-    <row r="66"/>
-    <row r="67"/>
-    <row r="68"/>
-    <row r="69"/>
-    <row r="70"/>
-    <row r="71"/>
-    <row r="72"/>
-    <row r="73"/>
-    <row r="74"/>
-    <row r="75"/>
-    <row r="76"/>
-    <row r="77"/>
-    <row r="78"/>
-    <row r="79"/>
-    <row r="80"/>
-    <row r="81"/>
-    <row r="82"/>
-    <row r="83"/>
-    <row r="84"/>
-    <row r="85"/>
-    <row r="86"/>
-    <row r="87"/>
-    <row r="88"/>
-    <row r="89"/>
-    <row r="90"/>
-    <row r="91"/>
-    <row r="92"/>
-    <row r="93"/>
-    <row r="94"/>
-    <row r="95"/>
-    <row r="96"/>
-    <row r="97"/>
-    <row r="98"/>
-    <row r="99"/>
-    <row r="100"/>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:Q7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Manualisasi forward pass + softmax TomBERT (contoh, dataset Twitter2015)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>id_sample</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>true_label_id</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>true_label_name</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>pred_label_id</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>pred_label_name</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>logit_neg_z0</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>logit_neu_z1</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>logit_pos_z2</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>exp_z0</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>exp_z1</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>exp_z2</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>sum_exp</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>p_neg</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>p_neu</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>p_pos</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>pred_label_from_softmax</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>RT @ OU Football : Practice one in the books Want more photos ? Follow the official $T$ football Facebook page ! # onlyONE</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="I3" t="n">
+        <v>-1.8</v>
+      </c>
+      <c r="J3">
+        <f>EXP(G2)</f>
+        <v/>
+      </c>
+      <c r="K3">
+        <f>EXP(H2)</f>
+        <v/>
+      </c>
+      <c r="L3">
+        <f>EXP(I2)</f>
+        <v/>
+      </c>
+      <c r="M3">
+        <f>J2+K2+L2</f>
+        <v/>
+      </c>
+      <c r="N3">
+        <f>J2/M2</f>
+        <v/>
+      </c>
+      <c r="O3">
+        <f>K2/M2</f>
+        <v/>
+      </c>
+      <c r="P3">
+        <f>L2/M2</f>
+        <v/>
+      </c>
+      <c r="Q3">
+        <f>IF(N2=MAX(N2:P2),0,IF(O2=MAX(N2:P2),1,2))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Crazy hair day ! $T$ is a contender . : )</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>2</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>2</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="I4" t="n">
+        <v>-1.8</v>
+      </c>
+      <c r="J4">
+        <f>EXP(G3)</f>
+        <v/>
+      </c>
+      <c r="K4">
+        <f>EXP(H3)</f>
+        <v/>
+      </c>
+      <c r="L4">
+        <f>EXP(I3)</f>
+        <v/>
+      </c>
+      <c r="M4">
+        <f>J3+K3+L3</f>
+        <v/>
+      </c>
+      <c r="N4">
+        <f>J3/M3</f>
+        <v/>
+      </c>
+      <c r="O4">
+        <f>K3/M3</f>
+        <v/>
+      </c>
+      <c r="P4">
+        <f>L3/M3</f>
+        <v/>
+      </c>
+      <c r="Q4">
+        <f>IF(N3=MAX(N3:P3),0,IF(O3=MAX(N3:P3),1,2))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>RT @ HistoryNeedsYou : Mother and child # art for # MothersDay by $T$ , 1934</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="I5" t="n">
+        <v>-1.8</v>
+      </c>
+      <c r="J5">
+        <f>EXP(G4)</f>
+        <v/>
+      </c>
+      <c r="K5">
+        <f>EXP(H4)</f>
+        <v/>
+      </c>
+      <c r="L5">
+        <f>EXP(I4)</f>
+        <v/>
+      </c>
+      <c r="M5">
+        <f>J4+K4+L4</f>
+        <v/>
+      </c>
+      <c r="N5">
+        <f>J4/M4</f>
+        <v/>
+      </c>
+      <c r="O5">
+        <f>K4/M4</f>
+        <v/>
+      </c>
+      <c r="P5">
+        <f>L4/M4</f>
+        <v/>
+      </c>
+      <c r="Q5">
+        <f>IF(N4=MAX(N4:P4),0,IF(O4=MAX(N4:P4),1,2))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>4</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Detailed illustrations of mythical creatures by $T$</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="I6" t="n">
+        <v>-1.8</v>
+      </c>
+      <c r="J6">
+        <f>EXP(G5)</f>
+        <v/>
+      </c>
+      <c r="K6">
+        <f>EXP(H5)</f>
+        <v/>
+      </c>
+      <c r="L6">
+        <f>EXP(I5)</f>
+        <v/>
+      </c>
+      <c r="M6">
+        <f>J5+K5+L5</f>
+        <v/>
+      </c>
+      <c r="N6">
+        <f>J5/M5</f>
+        <v/>
+      </c>
+      <c r="O6">
+        <f>K5/M5</f>
+        <v/>
+      </c>
+      <c r="P6">
+        <f>L5/M5</f>
+        <v/>
+      </c>
+      <c r="Q6">
+        <f>IF(N5=MAX(N5:P5),0,IF(O5=MAX(N5:P5),1,2))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>5</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>RT @ bohemianizm : Art from $T$ # art # visualart # craft</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="I7" t="n">
+        <v>-1.8</v>
+      </c>
+      <c r="J7">
+        <f>EXP(G6)</f>
+        <v/>
+      </c>
+      <c r="K7">
+        <f>EXP(H6)</f>
+        <v/>
+      </c>
+      <c r="L7">
+        <f>EXP(I6)</f>
+        <v/>
+      </c>
+      <c r="M7">
+        <f>J6+K6+L6</f>
+        <v/>
+      </c>
+      <c r="N7">
+        <f>J6/M6</f>
+        <v/>
+      </c>
+      <c r="O7">
+        <f>K6/M6</f>
+        <v/>
+      </c>
+      <c r="P7">
+        <f>L6/M6</f>
+        <v/>
+      </c>
+      <c r="Q7">
+        <f>IF(N6=MAX(N6:P6),0,IF(O6=MAX(N6:P6),1,2))</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
